--- a/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1363,6 +1363,37 @@
         <v>0</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>override_array</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>150</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>codex.signal.override_array</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1394,6 +1394,37 @@
         <v>0</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>sim_lab</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>100</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>codex.research.lab</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1425,6 +1425,37 @@
         <v>0</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>test_range</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>120</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>12</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>codex.research.range</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1456,6 +1456,37 @@
         <v>0</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>circuit_synth</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>100</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>10</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>codex.research.fusion</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1487,6 +1487,37 @@
         <v>0</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>listening_post</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>100</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>10</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>codex.intel.listening_post</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1518,6 +1518,37 @@
         <v>0</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>blackbox_gallery</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>100</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>codex.blackbox.gallery</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1549,6 +1549,68 @@
         <v>0</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>turret_light</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>150</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>10</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>codex.defense.turret</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>turret_heavy</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>260</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>14</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>codex.defense.turret</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1611,6 +1611,192 @@
         <v>0</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>barrier_t1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>120</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>6</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>codex.defense.barrier</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>barrier_t2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>260</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>8</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>codex.defense.barrier</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>barrier_t3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>480</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>codex.defense.barrier</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>gate</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>220</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>8</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>codex.defense.barrier</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>shield_gen</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>180</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>12</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>codex.defense.shield</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trap_emitter</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>120</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>8</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>codex.defense.trap</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1797,6 +1797,37 @@
         <v>0</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>repair_drone_station</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>220</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" t="n">
+        <v>12</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>codex.defense.repair_drone</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1828,6 +1828,37 @@
         <v>0</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>100</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>10</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>codex.env.purification</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1832,30 +1832,61 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
+          <t>drop_station</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>400</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="n">
+        <v>20</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>codex.expedition.drop</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>purifier</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>100</v>
-      </c>
-      <c r="D45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" t="n">
+      <c r="C46" t="n">
+        <v>100</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="n">
         <v>10</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>codex.env.purification</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
+++ b/Configs/GameConfig/Datas/fg/#BuildingService-建筑通用.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
